--- a/estimate_forms/031_vehicle_cleaner_estimate_form--estimate_forms.xlsx
+++ b/estimate_forms/031_vehicle_cleaner_estimate_form--estimate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'truck'}</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Truck'}</t>
+          <t>Truck</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'suv'}</t>
+          <t>suv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'SUV'}</t>
+          <t>SUV</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'4',_'label':_'van'}</t>
+          <t>van</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '4', 'label': 'Van'}</t>
+          <t>Van</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'basic_wash'}</t>
+          <t>basic_wash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Basic Wash'}</t>
+          <t>Basic Wash</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'advanced_wash'}</t>
+          <t>advanced_wash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Advanced Wash'}</t>
+          <t>Advanced Wash</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'full_detail'}</t>
+          <t>full_detail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Full Detail'}</t>
+          <t>Full Detail</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'4',_'label':_'interior_clean'}</t>
+          <t>interior_clean</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '4', 'label': 'Interior Clean'}</t>
+          <t>Interior Clean</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'5',_'label':_'exterior_clean'}</t>
+          <t>exterior_clean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '5', 'label': 'Exterior Clean'}</t>
+          <t>Exterior Clean</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'1',_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '1', 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'2',_'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '2', 'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'3',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '3', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
